--- a/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -500,12 +500,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -542,27 +542,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -574,32 +574,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -648,32 +648,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
     </row>
@@ -685,32 +685,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 13:57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 15:26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:28</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:15</t>
+          <t>4/5/2026 12:30</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:43</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,17 +811,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 14:47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 13:27</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:28</t>
+          <t>4/5/2026 13:22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:21</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:46</t>
+          <t>4/5/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -870,27 +870,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 14:14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 14:30</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 14:54</t>
+          <t>4/5/2026 10:18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 15:26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:46</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:11</t>
+          <t>4/5/2026 13:52</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 14:13</t>
         </is>
       </c>
     </row>
@@ -1055,22 +1055,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:52</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 15:26</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:25</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:20</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 15:17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:43</t>
+          <t>4/5/2026 08:22</t>
         </is>
       </c>
     </row>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:17</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:03</t>
+          <t>4/5/2026 15:21</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 11:20</t>
+          <t>4/5/2026 15:17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:24</t>
+          <t>4/5/2026 10:26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>360161 / 19152</t>
+          <t>343361 / 18552</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.7340 sec</t>
+          <t>5.1180 sec</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.09</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="34">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11.82</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="36">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.18</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="37">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="38">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.3</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="40">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37.73</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="41">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>20.96</v>
+        <v>33.54</v>
       </c>
     </row>
   </sheetData>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
@@ -468,27 +468,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
     </row>
@@ -500,12 +500,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 14:56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 06:03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 06:33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
     </row>
@@ -579,27 +579,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -611,22 +611,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 15:14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
     </row>
@@ -685,32 +685,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 13:57</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 10:00</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:26</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:48</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 12:30</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 14:47</t>
+          <t>4/5/2026 07:26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 14:45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:30</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 12:28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 13:47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 14:14</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 14:30</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:18</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:35</t>
+          <t>4/5/2026 06:16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:26</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 12:36</t>
+          <t>4/5/2026 13:34</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 13:52</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:18</t>
+          <t>4/5/2026 14:40</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:31</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 14:13</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>4/5/2026 09:52</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Infeed Station 3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>4/5/2026 09:13</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Infeed Station 1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4/5/2026 15:26</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 14:11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
     </row>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:17</t>
+          <t>4/5/2026 13:20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:22</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
     </row>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 15:05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:21</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:17</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>423.67 min</t>
+          <t>427.67 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.73 min</t>
+          <t>35.95 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>82.33 min</t>
+          <t>87.33 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86.00 min</t>
+          <t>91.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.00 min</t>
+          <t>27.00 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.00/0.00/0.00 min</t>
+          <t>10.00/7.00/10.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>343361 / 18552</t>
+          <t>332504 / 18288</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5.1180 sec</t>
+          <t>10.2350 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.0000 %</t>
+          <t>1.5709 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30.57 min | 86.00 min</t>
+          <t>33.76 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28.86 min | 76.00 min</t>
+          <t>38.14 min | 91.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29.76 min | 85.00 min</t>
+          <t>35.95 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.18</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="34">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.55</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.18</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="36">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.73</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="37">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.38</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="38">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="40">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25.15</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="41">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.35</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="42">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33.54</v>
+        <v>37.38</v>
       </c>
     </row>
   </sheetData>
@@ -1774,22 +1774,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 11:19</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2168,48 +2168,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 10:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:44</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2888,48 +2888,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -3008,48 +3008,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:04</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -3128,48 +3128,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:12</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-0</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 06:05</t>
+          <t>4/5/2026 06:32</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -3321,35 +3321,35 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3394,22 +3394,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3428,48 +3428,48 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 10:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -3694,22 +3694,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:46</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3728,48 +3728,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -3814,22 +3814,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3848,48 +3848,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:24</t>
+          <t>4/5/2026 07:34</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:24</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:42</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:50</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M37" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -3934,22 +3934,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4028,25 +4028,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4054,22 +4054,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -4088,48 +4088,48 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:20</t>
+          <t>4/5/2026 08:30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
@@ -4161,35 +4161,35 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M42" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -4221,35 +4221,35 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 11:33</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -4448,48 +4448,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M50" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -4748,48 +4748,48 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M52" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53">
@@ -4808,48 +4808,48 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -4894,22 +4894,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -5108,48 +5108,48 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:22</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:22</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -5194,22 +5194,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -5494,22 +5494,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_3_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.2350 sec</t>
+          <t>9.9990 sec</t>
         </is>
       </c>
     </row>
